--- a/ig/DM-FEVRIER-2026/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
+++ b/ig/DM-FEVRIER-2026/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="91">
   <si>
     <t>Property</t>
   </si>
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20250411120000</t>
+    <t>20260223120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-11T12:00:00+01:00</t>
+    <t>2026-02-23T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -162,6 +162,9 @@
     <t>112</t>
   </si>
   <si>
+    <t>136</t>
+  </si>
+  <si>
     <t>37</t>
   </si>
   <si>
@@ -211,9 +214,6 @@
   </si>
   <si>
     <t>135</t>
-  </si>
-  <si>
-    <t>136</t>
   </si>
   <si>
     <t>146</t>
@@ -539,7 +539,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E78"/>
+  <dimension ref="A1:E79"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -760,27 +760,27 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B17" s="2"/>
       <c r="C17" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D17" t="s" s="2">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E17" s="2"/>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B18" s="2"/>
       <c r="C18" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D18" t="s" s="2">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="E18" s="2"/>
     </row>
@@ -793,33 +793,33 @@
         <v>32</v>
       </c>
       <c r="D19" t="s" s="2">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E19" s="2"/>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B20" s="2"/>
       <c r="C20" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D20" t="s" s="2">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E20" s="2"/>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="B21" s="2"/>
       <c r="C21" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D21" t="s" s="2">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E21" s="2"/>
     </row>
@@ -962,20 +962,20 @@
         <v>32</v>
       </c>
       <c r="D32" t="s" s="2">
-        <v>41</v>
+        <v>62</v>
       </c>
       <c r="E32" s="2"/>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B33" s="2"/>
       <c r="C33" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D33" t="s" s="2">
-        <v>62</v>
+        <v>41</v>
       </c>
       <c r="E33" s="2"/>
     </row>
@@ -1001,7 +1001,7 @@
         <v>32</v>
       </c>
       <c r="D35" t="s" s="2">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="E35" s="2"/>
     </row>
@@ -1014,7 +1014,7 @@
         <v>32</v>
       </c>
       <c r="D36" t="s" s="2">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E36" s="2"/>
     </row>
@@ -1053,7 +1053,7 @@
         <v>32</v>
       </c>
       <c r="D39" t="s" s="2">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="E39" s="2"/>
     </row>
@@ -1066,33 +1066,33 @@
         <v>32</v>
       </c>
       <c r="D40" t="s" s="2">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E40" s="2"/>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B41" s="2"/>
       <c r="C41" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D41" t="s" s="2">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E41" s="2"/>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>70</v>
+        <v>35</v>
       </c>
       <c r="B42" s="2"/>
       <c r="C42" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D42" t="s" s="2">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E42" s="2"/>
     </row>
@@ -1105,7 +1105,7 @@
         <v>32</v>
       </c>
       <c r="D43" t="s" s="2">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E43" s="2"/>
     </row>
@@ -1118,7 +1118,7 @@
         <v>32</v>
       </c>
       <c r="D44" t="s" s="2">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E44" s="2"/>
     </row>
@@ -1131,20 +1131,20 @@
         <v>32</v>
       </c>
       <c r="D45" t="s" s="2">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E45" s="2"/>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="B46" s="2"/>
       <c r="C46" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D46" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E46" s="2"/>
     </row>
@@ -1157,7 +1157,7 @@
         <v>32</v>
       </c>
       <c r="D47" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E47" s="2"/>
     </row>
@@ -1170,72 +1170,72 @@
         <v>32</v>
       </c>
       <c r="D48" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E48" s="2"/>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="B49" s="2"/>
       <c r="C49" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D49" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E49" s="2"/>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B50" s="2"/>
       <c r="C50" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D50" t="s" s="2">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E50" s="2"/>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B51" s="2"/>
       <c r="C51" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D51" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E51" s="2"/>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B52" s="2"/>
       <c r="C52" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D52" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E52" s="2"/>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="B53" s="2"/>
       <c r="C53" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D53" t="s" s="2">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E53" s="2"/>
     </row>
@@ -1248,7 +1248,7 @@
         <v>32</v>
       </c>
       <c r="D54" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E54" s="2"/>
     </row>
@@ -1261,20 +1261,20 @@
         <v>32</v>
       </c>
       <c r="D55" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E55" s="2"/>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>85</v>
+        <v>37</v>
       </c>
       <c r="B56" s="2"/>
       <c r="C56" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D56" t="s" s="2">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E56" s="2"/>
     </row>
@@ -1287,7 +1287,7 @@
         <v>32</v>
       </c>
       <c r="D57" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E57" s="2"/>
     </row>
@@ -1300,20 +1300,20 @@
         <v>32</v>
       </c>
       <c r="D58" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E58" s="2"/>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="B59" s="2"/>
       <c r="C59" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D59" t="s" s="2">
-        <v>36</v>
+        <v>88</v>
       </c>
       <c r="E59" s="2"/>
     </row>
@@ -1326,7 +1326,7 @@
         <v>32</v>
       </c>
       <c r="D60" t="s" s="2">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="E60" s="2"/>
     </row>
@@ -1456,7 +1456,7 @@
         <v>32</v>
       </c>
       <c r="D70" t="s" s="2">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="E70" s="2"/>
     </row>
@@ -1469,7 +1469,7 @@
         <v>32</v>
       </c>
       <c r="D71" t="s" s="2">
-        <v>61</v>
+        <v>41</v>
       </c>
       <c r="E71" s="2"/>
     </row>
@@ -1482,20 +1482,20 @@
         <v>32</v>
       </c>
       <c r="D72" t="s" s="2">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="E72" s="2"/>
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B73" s="2"/>
       <c r="C73" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D73" t="s" s="2">
-        <v>47</v>
+        <v>69</v>
       </c>
       <c r="E73" s="2"/>
     </row>
@@ -1508,7 +1508,7 @@
         <v>32</v>
       </c>
       <c r="D74" t="s" s="2">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E74" s="2"/>
     </row>
@@ -1521,7 +1521,7 @@
         <v>32</v>
       </c>
       <c r="D75" t="s" s="2">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E75" s="2"/>
     </row>
@@ -1534,7 +1534,7 @@
         <v>32</v>
       </c>
       <c r="D76" t="s" s="2">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="E76" s="2"/>
     </row>
@@ -1547,7 +1547,7 @@
         <v>32</v>
       </c>
       <c r="D77" t="s" s="2">
-        <v>80</v>
+        <v>41</v>
       </c>
       <c r="E77" s="2"/>
     </row>
@@ -1560,9 +1560,22 @@
         <v>32</v>
       </c>
       <c r="D78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E78" s="2"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="B79" s="2"/>
+      <c r="C79" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D79" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="E78" s="2"/>
+      <c r="E79" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
